--- a/public/downloads/inventory-tracker.xlsx
+++ b/public/downloads/inventory-tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Explore Excel\Explore Excel Updated\explore-excel-complete\explore-excel\public\downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{412ADE50-90EE-410A-A0AF-F0A28D27D885}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C78A6FE3-D8DC-469F-AF00-C1E52EECF49E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="23040" windowHeight="12684" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3573,16 +3573,16 @@
       <c r="F133" s="4"/>
       <c r="G133" s="4"/>
       <c r="H133" s="5" t="str">
-        <f t="shared" ref="H133:H164" si="12">IF(A133="","",N(E133)+N(F133)-N(G133))</f>
+        <f t="shared" ref="H133:H154" si="12">IF(A133="","",N(E133)+N(F133)-N(G133))</f>
         <v/>
       </c>
       <c r="I133" s="6" t="str">
-        <f t="shared" ref="I133:I164" si="13">IF(H133="","",H133*N(D133))</f>
+        <f t="shared" ref="I133:I154" si="13">IF(H133="","",H133*N(D133))</f>
         <v/>
       </c>
       <c r="J133" s="4"/>
       <c r="K133" s="7" t="str">
-        <f t="shared" ref="K133:K164" si="14">IF(A133="","",IF(H133&lt;=0,"Out of stock",IF(H133&lt;=N(J133),"Reorder","OK")))</f>
+        <f t="shared" ref="K133:K154" si="14">IF(A133="","",IF(H133&lt;=0,"Out of stock",IF(H133&lt;=N(J133),"Reorder","OK")))</f>
         <v/>
       </c>
     </row>
@@ -4370,7 +4370,7 @@
       <c r="B13" s="24"/>
       <c r="C13" s="24"/>
     </row>
-    <row r="14" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" ht="42.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="25" t="s">
         <v>47</v>
       </c>
@@ -4384,7 +4384,7 @@
       <c r="B16" s="24"/>
       <c r="C16" s="24"/>
     </row>
-    <row r="17" spans="1:3" ht="34.049999999999997" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:3" ht="42.3" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="25" t="s">
         <v>49</v>
       </c>
@@ -4393,6 +4393,10 @@
     </row>
   </sheetData>
   <mergeCells count="12">
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A2:C2"/>
     <mergeCell ref="A16:C16"/>
     <mergeCell ref="A8:C8"/>
     <mergeCell ref="A14:C14"/>
@@ -4401,10 +4405,6 @@
     <mergeCell ref="A10:C10"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="A11:C11"/>
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
-    <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A2:C2"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
